--- a/Sec_Work/Performance Estimation.xlsx
+++ b/Sec_Work/Performance Estimation.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdti365-my.sharepoint.com/personal/6610301008_ms_cdti_ac_th/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{3B1FFE63-8102-ED40-83F9-1FB714214CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7FCDE29-D610-43D3-8C40-60B19E239FF3}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{3B1FFE63-8102-ED40-83F9-1FB714214CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3176CE1A-1A7F-9D43-A359-B984811DDF91}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E08599C0-2E70-4653-8C2D-3503B5FB7A02}"/>
+    <workbookView xWindow="820" yWindow="1540" windowWidth="21780" windowHeight="14500" activeTab="4" xr2:uid="{E08599C0-2E70-4653-8C2D-3503B5FB7A02}"/>
   </bookViews>
   <sheets>
     <sheet name="Holdout_L1" sheetId="1" r:id="rId1"/>
     <sheet name="k-fold_Cross-Validation_L2" sheetId="2" r:id="rId2"/>
     <sheet name="Holdout_L3" sheetId="3" r:id="rId3"/>
     <sheet name="k-fold_Cross-Validation_L3" sheetId="4" r:id="rId4"/>
+    <sheet name="Reference_RMSE_5.54_L4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
   <si>
     <t>Seed</t>
   </si>
@@ -67,6 +68,15 @@
   <si>
     <t>20-fold</t>
   </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>10-fold CV</t>
+  </si>
+  <si>
+    <t>Holdout 90%</t>
+  </si>
 </sst>
 </file>
 
@@ -89,7 +99,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -213,11 +223,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -247,7 +266,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -257,11 +275,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -597,9 +621,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA29373-E774-4D83-8CD8-0D6BDEFA6620}">
   <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -619,7 +643,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B3" s="7">
         <v>1</v>
       </c>
@@ -639,7 +663,7 @@
         <v>18.349299999999999</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="7">
         <v>2</v>
       </c>
@@ -659,7 +683,7 @@
         <v>11.5359</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B5" s="7">
         <v>3</v>
       </c>
@@ -679,7 +703,7 @@
         <v>30.436299999999999</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6" s="7">
         <v>4</v>
       </c>
@@ -699,7 +723,7 @@
         <v>33.031399999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" s="7">
         <v>5</v>
       </c>
@@ -719,7 +743,7 @@
         <v>32.265599999999999</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="7">
         <v>6</v>
       </c>
@@ -739,7 +763,7 @@
         <v>16.208100000000002</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="7">
         <v>7</v>
       </c>
@@ -759,7 +783,7 @@
         <v>18.619</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
         <v>8</v>
       </c>
@@ -779,7 +803,7 @@
         <v>23.744800000000001</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
         <v>9</v>
       </c>
@@ -799,7 +823,7 @@
         <v>18.229199999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
         <v>10</v>
       </c>
@@ -819,53 +843,53 @@
         <v>9.5061</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="15">
         <f>AVERAGE(C3:C12)</f>
         <v>8.1296199999999992</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <f t="shared" ref="D13:G13" si="0">AVERAGE(D3:D12)</f>
         <v>7.4573200000000002</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <f t="shared" si="0"/>
         <v>7.4137209999999998</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <f t="shared" si="0"/>
         <v>10.917422999999999</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="16">
         <f t="shared" si="0"/>
         <v>21.19257</v>
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <f>_xlfn.STDEV.S(C3:C13)</f>
         <v>1.591856754108232</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <f t="shared" ref="D14:G14" si="1">_xlfn.STDEV.S(D3:D13)</f>
         <v>1.1157922304802121</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <f t="shared" si="1"/>
         <v>0.71720179794044026</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <f t="shared" si="1"/>
         <v>3.7943486807304612</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="18">
         <f t="shared" si="1"/>
         <v>7.9554328465583835</v>
       </c>
@@ -876,16 +900,15 @@
   <headerFooter>
     <oddHeader>&amp;C&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CA4ED9-1B54-5348-B76C-B365C7487AA4}">
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -902,7 +925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="7">
         <v>1</v>
       </c>
@@ -919,7 +942,7 @@
         <v>8.0958000000000006</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="7">
         <v>2</v>
       </c>
@@ -936,7 +959,7 @@
         <v>6.8631000000000002</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="7">
         <v>3</v>
       </c>
@@ -953,7 +976,7 @@
         <v>9.0195000000000007</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="7">
         <v>4</v>
       </c>
@@ -970,7 +993,7 @@
         <v>6.7549999999999999</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="7">
         <v>5</v>
       </c>
@@ -987,7 +1010,7 @@
         <v>7.1531000000000002</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="7">
         <v>6</v>
       </c>
@@ -1004,7 +1027,7 @@
         <v>7.0590000000000002</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="7">
         <v>7</v>
       </c>
@@ -1021,7 +1044,7 @@
         <v>7.5880999999999998</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
         <v>8</v>
       </c>
@@ -1038,7 +1061,7 @@
         <v>7.8343999999999996</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
         <v>9</v>
       </c>
@@ -1055,7 +1078,7 @@
         <v>8.9117999999999995</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
         <v>10</v>
       </c>
@@ -1072,44 +1095,44 @@
         <v>7.2911000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <f>AVERAGE(C3:C12)</f>
         <v>7.4989999999999997</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <f t="shared" ref="D13:F13" si="0">AVERAGE(D3:D12)</f>
         <v>7.5782800000000012</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <f t="shared" si="0"/>
         <v>7.73001</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>7.6570899999999993</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <f>_xlfn.STDEV.S(C3:C12)</f>
         <v>0.1586942973140498</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <f t="shared" ref="D14:F14" si="1">_xlfn.STDEV.S(D3:D12)</f>
         <v>0.67347385794352332</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <f t="shared" si="1"/>
         <v>0.78406782083354698</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <f t="shared" si="1"/>
         <v>0.80615519935335311</v>
       </c>
@@ -1119,26 +1142,25 @@
   <headerFooter>
     <oddHeader>&amp;C&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2B0476D-E7A2-EB44-A030-95644B78B815}">
   <dimension ref="B2:G14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="14">
         <v>0.9</v>
       </c>
       <c r="D2" s="3">
         <v>0.8</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>0.5</v>
       </c>
       <c r="F2" s="3">
@@ -1148,17 +1170,17 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3">
         <v>6.2987000000000002</v>
       </c>
       <c r="D3" s="10">
         <v>5.9325999999999999</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="4">
         <v>5.0979999999999999</v>
       </c>
       <c r="F3" s="10">
@@ -1168,17 +1190,17 @@
         <v>6.093</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4">
         <v>6.8886000000000003</v>
       </c>
       <c r="D4" s="10">
         <v>5.9005000000000001</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="4">
         <v>6.0854999999999997</v>
       </c>
       <c r="F4" s="10">
@@ -1188,17 +1210,17 @@
         <v>8.4732000000000003</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5">
         <v>5.5472999999999999</v>
       </c>
       <c r="D5" s="10">
         <v>6.5236999999999998</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="4">
         <v>6.2724000000000002</v>
       </c>
       <c r="F5" s="10">
@@ -1208,17 +1230,17 @@
         <v>6.1570999999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6">
         <v>5.9954000000000001</v>
       </c>
       <c r="D6" s="10">
         <v>5.6063000000000001</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="4">
         <v>6.0293999999999999</v>
       </c>
       <c r="F6" s="10">
@@ -1228,17 +1250,17 @@
         <v>6.9554999999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7">
         <v>5.4429999999999996</v>
       </c>
       <c r="D7" s="10">
         <v>5.1409000000000002</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="4">
         <v>6.1883999999999997</v>
       </c>
       <c r="F7" s="10">
@@ -1248,17 +1270,17 @@
         <v>6.7449000000000003</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8">
         <v>5.9207999999999998</v>
       </c>
       <c r="D8" s="10">
         <v>6.2267000000000001</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="4">
         <v>6.0305</v>
       </c>
       <c r="F8" s="10">
@@ -1268,17 +1290,17 @@
         <v>5.9413999999999998</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9">
         <v>6.1413000000000002</v>
       </c>
       <c r="D9" s="10">
         <v>5.7308000000000003</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="4">
         <v>5.5617000000000001</v>
       </c>
       <c r="F9" s="10">
@@ -1288,17 +1310,17 @@
         <v>6.6295000000000002</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10">
         <v>5.7656999999999998</v>
       </c>
       <c r="D10" s="10">
         <v>6.8285999999999998</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="4">
         <v>6.8090000000000002</v>
       </c>
       <c r="F10" s="10">
@@ -1308,17 +1330,17 @@
         <v>6.7481999999999998</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
         <v>9</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11">
         <v>5.2801999999999998</v>
       </c>
       <c r="D11" s="10">
         <v>4.6761999999999997</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="4">
         <v>5.8560999999999996</v>
       </c>
       <c r="F11" s="10">
@@ -1328,17 +1350,17 @@
         <v>6.7662000000000004</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12">
         <v>5.7225999999999999</v>
       </c>
       <c r="D12" s="10">
         <v>6.3552</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="4">
         <v>5.8651999999999997</v>
       </c>
       <c r="F12" s="10">
@@ -1348,52 +1370,52 @@
         <v>6.3209</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <f>AVERAGE(C3:C12)</f>
         <v>5.9003600000000009</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <f>AVERAGE(D3:D12)</f>
         <v>5.8921500000000009</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <f>AVERAGE(E3:E12)</f>
         <v>5.9796199999999997</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>AVERAGE(F3:F12)</f>
         <v>6.2742799999999992</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="18">
         <f>AVERAGE(G3:G12)</f>
         <v>6.6829899999999993</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <f>_xlfn.STDEV.S(C3:C12)</f>
         <v>0.46796906640408542</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <f t="shared" ref="D14:G14" si="0">_xlfn.STDEV.S(D3:D12)</f>
         <v>0.6458838857634398</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <f t="shared" si="0"/>
         <v>0.44891447787350819</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0.28306375724678473</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="13">
         <f t="shared" si="0"/>
         <v>0.71512991896578548</v>
       </c>
@@ -1403,26 +1425,25 @@
   <headerFooter>
     <oddHeader>&amp;C&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D157060-490C-F844-8E4C-6B7E068A35BC}">
   <dimension ref="B2:G14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="20" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="20" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1432,17 +1453,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3">
         <v>5.8704999999999998</v>
       </c>
       <c r="D3" s="10">
         <v>5.8937999999999997</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="4">
         <v>5.8268000000000004</v>
       </c>
       <c r="F3" s="10">
@@ -1452,17 +1473,17 @@
         <v>5.8122999999999996</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4">
         <v>5.8632</v>
       </c>
       <c r="D4" s="10">
         <v>5.8724999999999996</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="4">
         <v>5.8548999999999998</v>
       </c>
       <c r="F4" s="10">
@@ -1472,17 +1493,17 @@
         <v>6.2487000000000004</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5">
         <v>5.8343999999999996</v>
       </c>
       <c r="D5" s="10">
         <v>5.8723000000000001</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="4">
         <v>5.83</v>
       </c>
       <c r="F5" s="10">
@@ -1492,17 +1513,17 @@
         <v>5.8998999999999997</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6">
         <v>5.8183999999999996</v>
       </c>
       <c r="D6" s="10">
         <v>5.8471000000000002</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="4">
         <v>5.8407999999999998</v>
       </c>
       <c r="F6" s="10">
@@ -1512,17 +1533,17 @@
         <v>5.8258999999999999</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="7">
         <v>5</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7">
         <v>5.8078000000000003</v>
       </c>
       <c r="D7" s="10">
         <v>5.8263999999999996</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="4">
         <v>5.8719000000000001</v>
       </c>
       <c r="F7" s="10">
@@ -1532,17 +1553,17 @@
         <v>6.1912000000000003</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8">
         <v>5.8231000000000002</v>
       </c>
       <c r="D8" s="10">
         <v>5.8028000000000004</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="4">
         <v>5.8000999999999996</v>
       </c>
       <c r="F8" s="10">
@@ -1552,17 +1573,17 @@
         <v>5.7767999999999997</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="7">
         <v>7</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9">
         <v>5.8665000000000003</v>
       </c>
       <c r="D9" s="10">
         <v>5.8616000000000001</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="4">
         <v>5.9787999999999997</v>
       </c>
       <c r="F9" s="10">
@@ -1572,17 +1593,17 @@
         <v>5.7290999999999999</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10">
         <v>5.8506999999999998</v>
       </c>
       <c r="D10" s="10">
         <v>5.91</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="4">
         <v>6.0442</v>
       </c>
       <c r="F10" s="10">
@@ -1592,17 +1613,17 @@
         <v>6.0342000000000002</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="7">
         <v>9</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11">
         <v>5.8329000000000004</v>
       </c>
       <c r="D11" s="10">
         <v>5.8163999999999998</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="4">
         <v>5.8224</v>
       </c>
       <c r="F11" s="10">
@@ -1612,17 +1633,17 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12">
         <v>5.8343999999999996</v>
       </c>
       <c r="D12" s="10">
         <v>5.7991000000000001</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="4">
         <v>5.8215000000000003</v>
       </c>
       <c r="F12" s="10">
@@ -1632,36 +1653,36 @@
         <v>5.7472000000000003</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <f>AVERAGE(C3:C12)</f>
         <v>5.8401900000000007</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <f t="shared" ref="D13:G13" si="0">AVERAGE(D3:D12)</f>
         <v>5.8502000000000001</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <f t="shared" si="0"/>
         <v>5.8691399999999998</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>5.8733400000000007</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="18">
         <f t="shared" si="0"/>
         <v>5.9185300000000005</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <f>_xlfn.STDEV.S(C3:C12)</f>
         <v>2.1569033873176189E-2</v>
       </c>
@@ -1669,7 +1690,7 @@
         <f t="shared" ref="D14:G14" si="1">_xlfn.STDEV.S(D3:D12)</f>
         <v>3.8252262097234868E-2</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <f t="shared" si="1"/>
         <v>7.9043029069263526E-2</v>
       </c>
@@ -1687,7 +1708,204 @@
   <headerFooter>
     <oddHeader>&amp;C&amp;G</oddHeader>
   </headerFooter>
-  <legacyDrawingHF r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5133049-148E-1944-886C-C3FDBD236DCE}">
+  <dimension ref="B2:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="23">
+        <v>7.06</v>
+      </c>
+      <c r="D3" s="10">
+        <v>7.87</v>
+      </c>
+      <c r="E3" s="4">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4" s="23">
+        <v>5.53</v>
+      </c>
+      <c r="D4" s="10">
+        <v>6.02</v>
+      </c>
+      <c r="E4" s="4">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="7">
+        <v>3</v>
+      </c>
+      <c r="C5" s="23">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="D5" s="10">
+        <v>4.92</v>
+      </c>
+      <c r="E5" s="4">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="7">
+        <v>4</v>
+      </c>
+      <c r="C6" s="24">
+        <v>6.08</v>
+      </c>
+      <c r="D6" s="10">
+        <v>6.29</v>
+      </c>
+      <c r="E6" s="4">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="24">
+        <v>5.89</v>
+      </c>
+      <c r="D7" s="10">
+        <v>6.26</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="7">
+        <v>6</v>
+      </c>
+      <c r="C8" s="24">
+        <v>4.42</v>
+      </c>
+      <c r="D8" s="10">
+        <v>5.04</v>
+      </c>
+      <c r="E8" s="4">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="7">
+        <v>7</v>
+      </c>
+      <c r="C9" s="24">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D9" s="10">
+        <v>6.07</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="7">
+        <v>8</v>
+      </c>
+      <c r="C10" s="24">
+        <v>5.61</v>
+      </c>
+      <c r="D10" s="10">
+        <v>6.25</v>
+      </c>
+      <c r="E10" s="4">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="7">
+        <v>9</v>
+      </c>
+      <c r="C11" s="24">
+        <v>3.98</v>
+      </c>
+      <c r="D11" s="10">
+        <v>4.28</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="24">
+        <v>4.59</v>
+      </c>
+      <c r="D12" s="10">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="E12" s="4">
+        <v>8.93</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="19">
+        <f>AVERAGE(C3:C12)</f>
+        <v>5.2900000000000009</v>
+      </c>
+      <c r="D13" s="19">
+        <f t="shared" ref="D13:E13" si="0">AVERAGE(D3:D12)</f>
+        <v>5.8019999999999996</v>
+      </c>
+      <c r="E13" s="18">
+        <f t="shared" si="0"/>
+        <v>6.6169999999999991</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="19">
+        <f>_xlfn.STDEV.S(C3:C12)</f>
+        <v>0.9248783703817457</v>
+      </c>
+      <c r="D14" s="19">
+        <f t="shared" ref="D14:E14" si="1">_xlfn.STDEV.S(D3:D12)</f>
+        <v>1.0182315824779562</v>
+      </c>
+      <c r="E14" s="18">
+        <f t="shared" si="1"/>
+        <v>2.8446013194587891</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
